--- a/public/cash-flow-forecast-imperial.xlsx
+++ b/public/cash-flow-forecast-imperial.xlsx
@@ -399,9 +399,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
@@ -435,58 +435,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CASH INFLOW</v>
+        <v>OPENING BALANCE</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gross Sales - Retail</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Gross Sales - Online</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
+        <v>CASH INFLOW</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Other Income</v>
+        <v>Gross Sales - Retail</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -509,7 +491,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TOTAL INFLOW</v>
+        <v>Gross Sales - Online</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -532,63 +514,69 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>Other Income</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CASH OUTFLOW</v>
+        <v>TOTAL INFLOW</v>
+      </c>
+      <c r="B8">
+        <f>SUM(B5:B7)</f>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f>SUM(C5:C7)</f>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f>SUM(D5:D7)</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>SUM(E5:E7)</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f>SUM(F5:F7)</f>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f>SUM(G5:G7)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Salaries</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Marketing</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
+        <v>CASH OUTFLOW</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Admin Expenses</v>
+        <v>Salaries</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -611,7 +599,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Less: Depreciation (non-cash)</v>
+        <v>Marketing</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -634,7 +622,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TOTAL OUTFLOW</v>
+        <v>Admin Expenses</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -657,35 +645,132 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>Less: Depreciation (non-cash)</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>TOTAL OUTFLOW</v>
+      </c>
+      <c r="B15">
+        <f>SUM(B11:B14)</f>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f>SUM(C11:C14)</f>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f>SUM(D11:D14)</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f>SUM(E11:E14)</f>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f>SUM(F11:F14)</f>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f>SUM(G11:G14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>NET CASH FLOW</v>
+      </c>
+      <c r="B17">
+        <f>B8-B15</f>
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <f>C8-C15</f>
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <f>D8-D15</f>
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f>E8-E15</f>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f>F8-F15</f>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <f>G8-G15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>CLOSING BALANCE</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
+      <c r="B18">
+        <f>B2+B17</f>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <f>C2+C17</f>
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <f>D2+D17</f>
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f>E2+E17</f>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <f>F2+F17</f>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <f>G2+G17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Note: Each month closing should equal next month opening. Depreciation is included as outflow but represents non-cash — net cash flow reflects actual cash movement.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/cash-flow-forecast-imperial.xlsx
+++ b/public/cash-flow-forecast-imperial.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -408,6 +408,7 @@
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -415,21 +416,24 @@
         <v/>
       </c>
       <c r="B1" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C1" s="1">
         <v>46204</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>46235</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
         <v>46266</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>46296</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>46327</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>46357</v>
       </c>
     </row>
@@ -455,6 +459,9 @@
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -488,6 +495,9 @@
       <c r="G5">
         <v>0</v>
       </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -511,6 +521,9 @@
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -534,6 +547,9 @@
       <c r="G7">
         <v>0</v>
       </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -563,6 +579,10 @@
         <f>SUM(G5:G7)</f>
         <v>0</v>
       </c>
+      <c r="H8">
+        <f>SUM(H5:H7)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -596,6 +616,9 @@
       <c r="G11">
         <v>0</v>
       </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -619,6 +642,9 @@
       <c r="G12">
         <v>0</v>
       </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -642,6 +668,9 @@
       <c r="G13">
         <v>0</v>
       </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -665,6 +694,9 @@
       <c r="G14">
         <v>0</v>
       </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -694,6 +726,10 @@
         <f>SUM(G11:G14)</f>
         <v>0</v>
       </c>
+      <c r="H15">
+        <f>SUM(H11:H14)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -728,6 +764,10 @@
         <f>G8-G15</f>
         <v>0</v>
       </c>
+      <c r="H17">
+        <f>H8-H15</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -757,6 +797,10 @@
         <f>G2+G17</f>
         <v>0</v>
       </c>
+      <c r="H18">
+        <f>H2+H17</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -765,12 +809,12 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Note: Each month closing should equal next month opening. Depreciation is included as outflow but represents non-cash — net cash flow reflects actual cash movement.</v>
+        <v>Note: Each month closing should equal next month opening. Depreciation is included as outflow but represents non-cash.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H20"/>
   </ignoredErrors>
 </worksheet>
 </file>